--- a/확률및통계/13주차/통합 문서1.xlsx
+++ b/확률및통계/13주차/통합 문서1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026_class\확률및통계\13주차\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3718B1-CA3C-4C61-B65A-9C16E3145212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC367492-211F-41E1-B830-15BD2BE102D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{75832AE7-4A85-478C-960C-418FDC33B0CD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{75832AE7-4A85-478C-960C-418FDC33B0CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="32">
   <si>
     <t>복용량(x)</t>
   </si>
@@ -203,7 +203,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -214,6 +214,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
   </cellXfs>
@@ -234,6 +246,767 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>복용량</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>(x)  </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>잔차도</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$G$27:$G$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>1.8484107579462137</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-2.1515892420537863</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.1075794621026933</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-3.6332518337408271</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.374083129584351</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.62591687041564903</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.8850855745721304</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2.8557457212713899</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.1442542787286101</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.5965770171149103</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4211-48E1-ACC3-6E86F2F14B90}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1068635344"/>
+        <c:axId val="1068643984"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1068635344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US"/>
+                  <a:t>복용량</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR"/>
+                  <a:t>(x)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1068643984"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1068643984"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US"/>
+                  <a:t>잔차</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1068635344"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>복용량</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" altLang="ko-KR"/>
+              <a:t>(x) </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>선 적합도</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>지속시간(y)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>22</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-22D0-453C-9AA3-475A20ED484B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>예측치 지속시간(y)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$F$27:$F$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>7.1515892420537863</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.1515892420537863</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.8924205378973067</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12.633251833740827</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.374083129584351</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>15.374083129584351</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18.11491442542787</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>20.85574572127139</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.85574572127139</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>23.59657701711491</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-22D0-453C-9AA3-475A20ED484B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1068637264"/>
+        <c:axId val="1068674704"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1068637264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US"/>
+                  <a:t>복용량</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR"/>
+                  <a:t>(x)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1068674704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1068674704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="ko-KR" altLang="en-US"/>
+                  <a:t>지속시간</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="ko-KR"/>
+                  <a:t>(y)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1068637264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$I$27:$I$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>95</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$J$27:$J$36</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0924-48AA-9234-54C0217EFFCC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="836628576"/>
+        <c:axId val="836622816"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="836628576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="836622816"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="836622816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="836628576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
@@ -473,7 +1246,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
@@ -820,7 +1593,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
@@ -1053,6 +1826,119 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7BE212C-1D04-0B76-609A-5883798A5937}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="차트 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D962FDD-D3FF-59CA-BDE8-C5762BD1040E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>298450</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="차트 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA8B8ED3-A329-C178-6B6C-8297B58F72F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -1482,10 +2368,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A23D993-5776-423C-B432-390BA518BADC}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1493,7 +2379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>3</v>
       </c>
@@ -1501,15 +2387,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>3</v>
       </c>
       <c r="B3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4">
         <v>4</v>
       </c>
@@ -1517,55 +2406,89 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>5</v>
       </c>
       <c r="B5">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>6</v>
       </c>
       <c r="B6">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0.91015538282158248</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.82838282087910131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0.80693067348898895</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="4">
+        <v>2.8207448425890393</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="E10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1573,9 +2496,368 @@
         <v>22</v>
       </c>
     </row>
+    <row r="12" spans="1:10" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="E13" s="6"/>
+      <c r="F13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="E14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4">
+        <v>307.24718826405865</v>
+      </c>
+      <c r="H14" s="4">
+        <v>307.24718826405865</v>
+      </c>
+      <c r="I14" s="4">
+        <v>38.615379887838984</v>
+      </c>
+      <c r="J14" s="4">
+        <v>2.5546831340477665E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="E15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="4">
+        <v>8</v>
+      </c>
+      <c r="G15" s="4">
+        <v>63.652811735941306</v>
+      </c>
+      <c r="H15" s="4">
+        <v>7.9566014669926632</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="1:10" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="5">
+        <v>9</v>
+      </c>
+      <c r="G16" s="5">
+        <v>370.9</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="5:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="18" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E18" s="6"/>
+      <c r="F18" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="4">
+        <v>-1.0709046454767783</v>
+      </c>
+      <c r="G19" s="4">
+        <v>2.7509135938149809</v>
+      </c>
+      <c r="H19" s="4">
+        <v>-0.38929054256176848</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0.70721879730039494</v>
+      </c>
+      <c r="J19" s="4">
+        <v>-7.4145227684034811</v>
+      </c>
+      <c r="K19" s="4">
+        <v>5.2727134774499245</v>
+      </c>
+      <c r="L19" s="4">
+        <v>-7.4145227684034811</v>
+      </c>
+      <c r="M19" s="4">
+        <v>5.2727134774499245</v>
+      </c>
+    </row>
+    <row r="20" spans="5:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E20" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2.7408312958435213</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.44106454536530676</v>
+      </c>
+      <c r="H20" s="5">
+        <v>6.2141274438040774</v>
+      </c>
+      <c r="I20" s="5">
+        <v>2.5546831340477621E-4</v>
+      </c>
+      <c r="J20" s="5">
+        <v>1.7237346303391778</v>
+      </c>
+      <c r="K20" s="5">
+        <v>3.7579279613478649</v>
+      </c>
+      <c r="L20" s="5">
+        <v>1.7237346303391778</v>
+      </c>
+      <c r="M20" s="5">
+        <v>3.7579279613478649</v>
+      </c>
+    </row>
+    <row r="24" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="5:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="26" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>7.1515892420537863</v>
+      </c>
+      <c r="G27" s="4">
+        <v>1.8484107579462137</v>
+      </c>
+      <c r="I27" s="4">
+        <v>5</v>
+      </c>
+      <c r="J27" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E28" s="4">
+        <v>2</v>
+      </c>
+      <c r="F28" s="4">
+        <v>7.1515892420537863</v>
+      </c>
+      <c r="G28" s="4">
+        <v>-2.1515892420537863</v>
+      </c>
+      <c r="I28" s="4">
+        <v>15</v>
+      </c>
+      <c r="J28" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E29" s="4">
+        <v>3</v>
+      </c>
+      <c r="F29" s="4">
+        <v>9.8924205378973067</v>
+      </c>
+      <c r="G29" s="4">
+        <v>2.1075794621026933</v>
+      </c>
+      <c r="I29" s="4">
+        <v>25</v>
+      </c>
+      <c r="J29" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E30" s="4">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4">
+        <v>12.633251833740827</v>
+      </c>
+      <c r="G30" s="4">
+        <v>-3.6332518337408271</v>
+      </c>
+      <c r="I30" s="4">
+        <v>35</v>
+      </c>
+      <c r="J30" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E31" s="4">
+        <v>5</v>
+      </c>
+      <c r="F31" s="4">
+        <v>15.374083129584351</v>
+      </c>
+      <c r="G31" s="4">
+        <v>-1.374083129584351</v>
+      </c>
+      <c r="I31" s="4">
+        <v>45</v>
+      </c>
+      <c r="J31" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="5:13" x14ac:dyDescent="0.45">
+      <c r="E32" s="4">
+        <v>6</v>
+      </c>
+      <c r="F32" s="4">
+        <v>15.374083129584351</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0.62591687041564903</v>
+      </c>
+      <c r="I32" s="4">
+        <v>55</v>
+      </c>
+      <c r="J32" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E33" s="4">
+        <v>7</v>
+      </c>
+      <c r="F33" s="4">
+        <v>18.11491442542787</v>
+      </c>
+      <c r="G33" s="4">
+        <v>3.8850855745721304</v>
+      </c>
+      <c r="I33" s="4">
+        <v>65</v>
+      </c>
+      <c r="J33" s="4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E34" s="4">
+        <v>8</v>
+      </c>
+      <c r="F34" s="4">
+        <v>20.85574572127139</v>
+      </c>
+      <c r="G34" s="4">
+        <v>-2.8557457212713899</v>
+      </c>
+      <c r="I34" s="4">
+        <v>75</v>
+      </c>
+      <c r="J34" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="5:10" x14ac:dyDescent="0.45">
+      <c r="E35" s="4">
+        <v>9</v>
+      </c>
+      <c r="F35" s="4">
+        <v>20.85574572127139</v>
+      </c>
+      <c r="G35" s="4">
+        <v>3.1442542787286101</v>
+      </c>
+      <c r="I35" s="4">
+        <v>85</v>
+      </c>
+      <c r="J35" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="5:10" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E36" s="5">
+        <v>10</v>
+      </c>
+      <c r="F36" s="5">
+        <v>23.59657701711491</v>
+      </c>
+      <c r="G36" s="5">
+        <v>-1.5965770171149103</v>
+      </c>
+      <c r="I36" s="5">
+        <v>95</v>
+      </c>
+      <c r="J36" s="5">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J27:J36">
+    <sortCondition ref="J27"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
